--- a/plantilla-rutina-gymos.xlsx
+++ b/plantilla-rutina-gymos.xlsx
@@ -6,15 +6,17 @@
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Sesiones" sheetId="2" r:id="rId2"/>
     <sheet name="Rutina" sheetId="3" r:id="rId3"/>
-    <sheet name="_Catálogos" sheetId="4" r:id="rId4" state="hidden"/>
-    <sheet name="_GymOS" sheetId="5" r:id="rId5" state="veryHidden"/>
+    <sheet name="Biblioteca" sheetId="4" r:id="rId4"/>
+    <sheet name="_Catálogos" sheetId="5" r:id="rId5" state="hidden"/>
+    <sheet name="_GymOS" sheetId="6" r:id="rId6" state="veryHidden"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Instrucciones!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Instrucciones!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sesiones!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Rutina!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'_Catálogos'!$A$1:$A$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">_GymOS!$A$1:$B$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Biblioteca!$A$1:$L$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'_Catálogos'!$A$1:$A$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">_GymOS!$A$1:$B$3</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -408,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -456,24 +458,56 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Importación</v>
+        <v>Biblioteca</v>
       </c>
       <c r="B6" t="str">
-        <v>Importar prepara una propuesta. Tu rutina actual no cambiará hasta que la actives.</v>
+        <v>Selecciona ejercicios de Biblioteca: no inventes uno si allí existe una alternativa válida. Copia exactamente Ejercicio y _GymOS exercise en Rutina.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>IDs</v>
+      </c>
+      <c r="B7" t="str">
+        <v>No traduzcas, abrevies ni modifiques IDs. Si el ejercicio no aparece en Biblioteca, deja _GymOS exercise vacío y conserva su nombre para el flujo existente.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ChatGPT</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Puede ayudarte a rellenar Sesiones y Rutina, pero debe respetar nombres, IDs, columnas y estructura de esta plantilla.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Hojas protegidas</v>
+      </c>
+      <c r="B9" t="str">
+        <v>No cambies los nombres, cabeceras ni estructura de las hojas _Catálogos y _GymOS.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Importación</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Importar prepara una propuesta para revisar. Tu rutina actual solo cambiará cuando actives esa propuesta.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Errores</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B11" t="str">
         <v>GymOS indicará hoja, fila y columna para que puedas corregirlos.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:B11"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -634,6 +668,3870 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L101"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="34.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="48.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>_GymOS exercise</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Ejercicio</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Alias</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Patrón</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Subpatrón</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Músculos principales</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Músculos secundarios</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Equipamiento técnico</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Grupo visible</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Equipamiento visible</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Notas</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>bench-press</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Press de banca</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Press banca · Press con barra</v>
+      </c>
+      <c r="D2" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E2" t="str">
+        <v>barbell_flat_press</v>
+      </c>
+      <c r="F2" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G2" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H2" t="str">
+        <v>barbell · plates · bench · squat_rack</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Escápulas retraídas y pies firmes.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>dumbbell-bench-press</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Press de banca con mancuernas</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Press plano con mancuernas · Press mancuernas plano</v>
+      </c>
+      <c r="D3" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E3" t="str">
+        <v>dumbbell_flat_press</v>
+      </c>
+      <c r="F3" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G3" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H3" t="str">
+        <v>dumbbells · bench</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Mantén las muñecas neutras y controla la bajada.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>incline-barbell-press</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Press inclinado con barra</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Press inclinado barra</v>
+      </c>
+      <c r="D4" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E4" t="str">
+        <v>barbell_incline_press</v>
+      </c>
+      <c r="F4" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G4" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H4" t="str">
+        <v>barbell · plates · adjustable_bench · squat_rack</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Usa una inclinación moderada y evita elevar los hombros.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>incline-db-press</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Press inclinado con mancuernas</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Press inclinado mancuernas</v>
+      </c>
+      <c r="D5" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E5" t="str">
+        <v>dumbbell_incline_press</v>
+      </c>
+      <c r="F5" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G5" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H5" t="str">
+        <v>dumbbells · adjustable_bench</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Controla la bajada.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>decline-bench-press</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Press declinado con barra</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Press declinado</v>
+      </c>
+      <c r="D6" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E6" t="str">
+        <v>barbell_decline_press</v>
+      </c>
+      <c r="F6" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G6" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H6" t="str">
+        <v>barbell · plates · decline_bench</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Asegura bien las piernas y usa un recorrido controlado.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>machine-chest-press</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Press de pecho en máquina</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Press pecho máquina · Press en máquina</v>
+      </c>
+      <c r="D7" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E7" t="str">
+        <v>machine_chest_press</v>
+      </c>
+      <c r="F7" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G7" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H7" t="str">
+        <v>chest_press_machine</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Ajusta el asiento para que las empuñaduras queden a la altura del pecho.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>cable-chest-fly</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Aperturas en polea</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Cruce de poleas · Aperturas con cable</v>
+      </c>
+      <c r="D8" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E8" t="str">
+        <v>cable_chest_fly</v>
+      </c>
+      <c r="F8" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G8" t="str">
+        <v>anterior_deltoid</v>
+      </c>
+      <c r="H8" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Mantén una ligera flexión de codo y junta los brazos sin encoger hombros.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>pec-deck-fly</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Aperturas en peck deck</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Peck deck · Contractora de pecho · Aperturas máquina</v>
+      </c>
+      <c r="D9" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E9" t="str">
+        <v>machine_chest_fly</v>
+      </c>
+      <c r="F9" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G9" t="str">
+        <v>anterior_deltoid</v>
+      </c>
+      <c r="H9" t="str">
+        <v>pec_deck</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Apoya la espalda y evita adelantar los hombros.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>dumbbell-fly</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Aperturas con mancuernas</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Aperturas mancuernas</v>
+      </c>
+      <c r="D10" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E10" t="str">
+        <v>dumbbell_chest_fly</v>
+      </c>
+      <c r="F10" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G10" t="str">
+        <v>anterior_deltoid</v>
+      </c>
+      <c r="H10" t="str">
+        <v>dumbbells · bench</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L10" t="str">
+        <v>No bajes más allá de un rango cómodo para el hombro.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>push-up</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Flexiones</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Flexión de brazos · Lagartijas</v>
+      </c>
+      <c r="D11" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E11" t="str">
+        <v>bodyweight_push_up</v>
+      </c>
+      <c r="F11" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G11" t="str">
+        <v>triceps · anterior_deltoid · trunk</v>
+      </c>
+      <c r="H11" t="str">
+        <v>bodyweight</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Mantén el cuerpo alineado y los codos en una trayectoria cómoda.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>chest-dip</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fondos para pecho</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Fondos de pecho · Fondos inclinados</v>
+      </c>
+      <c r="D12" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E12" t="str">
+        <v>bodyweight_chest_dip</v>
+      </c>
+      <c r="F12" t="str">
+        <v>chest</v>
+      </c>
+      <c r="G12" t="str">
+        <v>triceps · anterior_deltoid</v>
+      </c>
+      <c r="H12" t="str">
+        <v>dip_station</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Pecho</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Inclina ligeramente el tronco y evita una profundidad dolorosa.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>lat-pulldown</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Jalón al pecho</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Jalón · Jalón polea</v>
+      </c>
+      <c r="D13" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E13" t="str">
+        <v>wide_grip_lat_pulldown</v>
+      </c>
+      <c r="F13" t="str">
+        <v>latissimus_dorsi</v>
+      </c>
+      <c r="G13" t="str">
+        <v>biceps · upper_back</v>
+      </c>
+      <c r="H13" t="str">
+        <v>lat_pulldown</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Lleva los codos hacia abajo.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>neutral-grip-lat-pulldown</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Jalón al pecho con agarre neutro</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Jalón neutro · Jalón agarre neutro</v>
+      </c>
+      <c r="D14" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E14" t="str">
+        <v>neutral_grip_lat_pulldown</v>
+      </c>
+      <c r="F14" t="str">
+        <v>latissimus_dorsi</v>
+      </c>
+      <c r="G14" t="str">
+        <v>biceps · upper_back</v>
+      </c>
+      <c r="H14" t="str">
+        <v>lat_pulldown</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Inicia el movimiento bajando las escápulas antes de flexionar los codos.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>pull-up</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Dominadas pronas</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Dominadas · Dominada prona</v>
+      </c>
+      <c r="D15" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E15" t="str">
+        <v>pronated_pull_up</v>
+      </c>
+      <c r="F15" t="str">
+        <v>latissimus_dorsi · upper_back</v>
+      </c>
+      <c r="G15" t="str">
+        <v>biceps · forearms</v>
+      </c>
+      <c r="H15" t="str">
+        <v>pull_up_bar</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Evita balancearte y termina con control escapular.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>assisted-pull-up</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Dominadas asistidas</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Dominada asistida · Dominadas en máquina asistida</v>
+      </c>
+      <c r="D16" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E16" t="str">
+        <v>assisted_pull_up</v>
+      </c>
+      <c r="F16" t="str">
+        <v>latissimus_dorsi · upper_back</v>
+      </c>
+      <c r="G16" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="H16" t="str">
+        <v>assisted_pullup_dip_machine</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Usa la mínima asistencia que permita repeticiones limpias.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>chin-up</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Dominadas supinas</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Dominada supina · Chin ups</v>
+      </c>
+      <c r="D17" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E17" t="str">
+        <v>supinated_chin_up</v>
+      </c>
+      <c r="F17" t="str">
+        <v>latissimus_dorsi</v>
+      </c>
+      <c r="G17" t="str">
+        <v>biceps · upper_back</v>
+      </c>
+      <c r="H17" t="str">
+        <v>pull_up_bar</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Mantén las costillas controladas y evita impulsarte.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>barbell-row</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Remo con barra</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Remo barra</v>
+      </c>
+      <c r="D18" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E18" t="str">
+        <v>barbell_bent_over_row</v>
+      </c>
+      <c r="F18" t="str">
+        <v>upper_back · latissimus_dorsi</v>
+      </c>
+      <c r="G18" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H18" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Mantén la espalda neutra.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>seated-cable-row</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Remo sentado en polea</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Remo en polea baja · Remo polea sentado</v>
+      </c>
+      <c r="D19" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E19" t="str">
+        <v>seated_cable_row</v>
+      </c>
+      <c r="F19" t="str">
+        <v>upper_back · latissimus_dorsi</v>
+      </c>
+      <c r="G19" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H19" t="str">
+        <v>seated_row</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Evita llevar el tronco hacia atrás para completar la repetición.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>machine-row</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Remo en máquina</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Remo máquina · Remo guiado</v>
+      </c>
+      <c r="D20" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E20" t="str">
+        <v>machine_supported_row</v>
+      </c>
+      <c r="F20" t="str">
+        <v>upper_back · latissimus_dorsi</v>
+      </c>
+      <c r="G20" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H20" t="str">
+        <v>row_machine</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Ajusta el apoyo para mantener el pecho estable.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>one-arm-dumbbell-row</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Remo con mancuerna a una mano</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Remo unilateral con mancuerna · Remo mancuerna</v>
+      </c>
+      <c r="D21" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E21" t="str">
+        <v>single_arm_dumbbell_row</v>
+      </c>
+      <c r="F21" t="str">
+        <v>latissimus_dorsi · upper_back</v>
+      </c>
+      <c r="G21" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H21" t="str">
+        <v>dumbbells · bench</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Mantén la pelvis estable y lleva el codo hacia la cadera.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>chest-supported-db-row</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Remo con mancuernas apoyado en banco</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Remo pecho apoyado · Remo inclinado con apoyo</v>
+      </c>
+      <c r="D22" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E22" t="str">
+        <v>chest_supported_dumbbell_row</v>
+      </c>
+      <c r="F22" t="str">
+        <v>upper_back · latissimus_dorsi</v>
+      </c>
+      <c r="G22" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H22" t="str">
+        <v>dumbbells · adjustable_bench</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Mantén el pecho apoyado y evita encoger los hombros.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>t-bar-row</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Remo en T</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Remo T · T bar row</v>
+      </c>
+      <c r="D23" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E23" t="str">
+        <v>t_bar_row</v>
+      </c>
+      <c r="F23" t="str">
+        <v>upper_back · latissimus_dorsi</v>
+      </c>
+      <c r="G23" t="str">
+        <v>biceps · posterior_deltoid</v>
+      </c>
+      <c r="H23" t="str">
+        <v>t_bar_row_machine</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Mantén el abdomen activo y no redondees la zona lumbar.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>straight-arm-pulldown</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Pullover en polea con brazos rectos</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Jalón brazos rectos · Pullover polea</v>
+      </c>
+      <c r="D24" t="str">
+        <v>vertical_pull</v>
+      </c>
+      <c r="E24" t="str">
+        <v>straight_arm_cable_pulldown</v>
+      </c>
+      <c r="F24" t="str">
+        <v>latissimus_dorsi</v>
+      </c>
+      <c r="G24" t="str">
+        <v>triceps · trunk</v>
+      </c>
+      <c r="H24" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Espalda</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Mantén los codos casi extendidos y mueve desde el hombro.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>face-pull</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Face pull</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Tirón a la cara · Facepull</v>
+      </c>
+      <c r="D25" t="str">
+        <v>shoulder_external_rotation</v>
+      </c>
+      <c r="E25" t="str">
+        <v>cable_face_pull</v>
+      </c>
+      <c r="F25" t="str">
+        <v>posterior_deltoid · rotator_cuff</v>
+      </c>
+      <c r="G25" t="str">
+        <v>upper_back · lower_traps</v>
+      </c>
+      <c r="H25" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Tira hacia la cara separando las manos y rotando externamente.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>back-squat</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sentadilla trasera</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Sentadilla con barra</v>
+      </c>
+      <c r="D26" t="str">
+        <v>squat</v>
+      </c>
+      <c r="E26" t="str">
+        <v>barbell_back_squat</v>
+      </c>
+      <c r="F26" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G26" t="str">
+        <v>hamstrings · trunk</v>
+      </c>
+      <c r="H26" t="str">
+        <v>barbell · plates · squat_rack</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Rodillas alineadas con los pies.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>front-squat</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Sentadilla frontal</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Sentadilla frontal con barra</v>
+      </c>
+      <c r="D27" t="str">
+        <v>squat</v>
+      </c>
+      <c r="E27" t="str">
+        <v>barbell_front_squat</v>
+      </c>
+      <c r="F27" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G27" t="str">
+        <v>trunk · upper_back</v>
+      </c>
+      <c r="H27" t="str">
+        <v>barbell · plates · squat_rack</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Mantén los codos altos y el tronco erguido.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>goblet-squat</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Sentadilla goblet</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Sentadilla copa · Goblet squat</v>
+      </c>
+      <c r="D28" t="str">
+        <v>squat</v>
+      </c>
+      <c r="E28" t="str">
+        <v>goblet_squat</v>
+      </c>
+      <c r="F28" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G28" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="H28" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Sujeta la carga cerca del pecho y mantén el pie completo apoyado.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>smith-squat</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sentadilla en máquina Smith</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Sentadilla Smith · Sentadilla multipower</v>
+      </c>
+      <c r="D29" t="str">
+        <v>squat</v>
+      </c>
+      <c r="E29" t="str">
+        <v>smith_machine_squat</v>
+      </c>
+      <c r="F29" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G29" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="H29" t="str">
+        <v>smith_machine · plates</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Coloca los pies donde puedas mantener una trayectoria cómoda.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>hack-squat</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Sentadilla hack</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Hack squat · Jaca</v>
+      </c>
+      <c r="D30" t="str">
+        <v>knee_dominant</v>
+      </c>
+      <c r="E30" t="str">
+        <v>machine_hack_squat</v>
+      </c>
+      <c r="F30" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G30" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="H30" t="str">
+        <v>hack_squat_machine</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Mantén la espalda apoyada y controla la profundidad.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>leg-press</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Prensa de piernas</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Prensa</v>
+      </c>
+      <c r="D31" t="str">
+        <v>knee_dominant</v>
+      </c>
+      <c r="E31" t="str">
+        <v>machine_leg_press</v>
+      </c>
+      <c r="F31" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G31" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="H31" t="str">
+        <v>leg_press</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L31" t="str">
+        <v>No bloquees las rodillas.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>bulgarian-split-squat</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Sentadilla búlgara</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Búlgara · Split squat búlgaro</v>
+      </c>
+      <c r="D32" t="str">
+        <v>unilateral_lower_body</v>
+      </c>
+      <c r="E32" t="str">
+        <v>rear_foot_elevated_split_squat</v>
+      </c>
+      <c r="F32" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G32" t="str">
+        <v>hamstrings · trunk</v>
+      </c>
+      <c r="H32" t="str">
+        <v>dumbbells · bench</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Mantén estable la rodilla delantera y controla la bajada.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>reverse-lunge</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Zancada hacia atrás</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Zancada inversa · Lunge atrás</v>
+      </c>
+      <c r="D33" t="str">
+        <v>unilateral_lower_body</v>
+      </c>
+      <c r="E33" t="str">
+        <v>reverse_lunge</v>
+      </c>
+      <c r="F33" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G33" t="str">
+        <v>hamstrings · trunk</v>
+      </c>
+      <c r="H33" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Da un paso suficiente para mantener el talón delantero apoyado.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>walking-lunge</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Zancadas caminando</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Zancadas andando · Walking lunges</v>
+      </c>
+      <c r="D34" t="str">
+        <v>unilateral_lower_body</v>
+      </c>
+      <c r="E34" t="str">
+        <v>walking_lunge</v>
+      </c>
+      <c r="F34" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G34" t="str">
+        <v>hamstrings · calves · trunk</v>
+      </c>
+      <c r="H34" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Mantén el tronco estable y evita pasos demasiado cortos.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>step-up</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Subida al cajón</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Step up · Subida a banco</v>
+      </c>
+      <c r="D35" t="str">
+        <v>unilateral_lower_body</v>
+      </c>
+      <c r="E35" t="str">
+        <v>weighted_step_up</v>
+      </c>
+      <c r="F35" t="str">
+        <v>quadriceps · glutes</v>
+      </c>
+      <c r="G35" t="str">
+        <v>hamstrings · calves</v>
+      </c>
+      <c r="H35" t="str">
+        <v>dumbbells · step</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Piernas</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Impúlsate con la pierna que está sobre el cajón.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>leg-extension</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Extensión de piernas</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Extensión de cuádriceps · Cuádriceps máquina</v>
+      </c>
+      <c r="D36" t="str">
+        <v>knee_extension</v>
+      </c>
+      <c r="E36" t="str">
+        <v>machine_knee_extension</v>
+      </c>
+      <c r="F36" t="str">
+        <v>quadriceps</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>leg_extension</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Cuádriceps</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Alinea la rodilla con el eje de la máquina.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>hip-thrust</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Hip thrust con barra</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Empuje de cadera con barra · Hip thrust</v>
+      </c>
+      <c r="D37" t="str">
+        <v>hip_extension</v>
+      </c>
+      <c r="E37" t="str">
+        <v>barbell_hip_thrust</v>
+      </c>
+      <c r="F37" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="G37" t="str">
+        <v>hamstrings · trunk</v>
+      </c>
+      <c r="H37" t="str">
+        <v>barbell · plates · bench</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Termina extendiendo la cadera sin hiperextender la zona lumbar.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>machine-hip-thrust</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Hip thrust en máquina</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Empuje de cadera en máquina</v>
+      </c>
+      <c r="D38" t="str">
+        <v>hip_extension</v>
+      </c>
+      <c r="E38" t="str">
+        <v>machine_hip_thrust</v>
+      </c>
+      <c r="F38" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="G38" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="H38" t="str">
+        <v>hip_thrust_machine</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Ajusta la almohadilla sobre la pelvis y controla la bajada.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>glute-bridge</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Puente de glúteos</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Puente de cadera · Glute bridge</v>
+      </c>
+      <c r="D39" t="str">
+        <v>hip_extension</v>
+      </c>
+      <c r="E39" t="str">
+        <v>bodyweight_glute_bridge</v>
+      </c>
+      <c r="F39" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="G39" t="str">
+        <v>hamstrings · trunk</v>
+      </c>
+      <c r="H39" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Aprieta glúteos arriba sin arquear la espalda.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>cable-kickback</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Extensión de cadera en polea</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Patada de glúteo en polea · Kickback en polea</v>
+      </c>
+      <c r="D40" t="str">
+        <v>hip_extension</v>
+      </c>
+      <c r="E40" t="str">
+        <v>standing_cable_hip_extension</v>
+      </c>
+      <c r="F40" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="G40" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="H40" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Extiende la cadera sin arquear la zona lumbar ni girar la pelvis.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>romanian-deadlift</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Peso muerto rumano</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Peso muerto rumano con barra</v>
+      </c>
+      <c r="D41" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E41" t="str">
+        <v>barbell_romanian_deadlift</v>
+      </c>
+      <c r="F41" t="str">
+        <v>hamstrings · glutes</v>
+      </c>
+      <c r="G41" t="str">
+        <v>spinal_erectors · forearms</v>
+      </c>
+      <c r="H41" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Desplaza la cadera atrás.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>db-romanian-deadlift</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Peso muerto rumano con mancuernas</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Rumano con mancuernas · RDL mancuernas</v>
+      </c>
+      <c r="D42" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E42" t="str">
+        <v>dumbbell_romanian_deadlift</v>
+      </c>
+      <c r="F42" t="str">
+        <v>hamstrings · glutes</v>
+      </c>
+      <c r="G42" t="str">
+        <v>spinal_erectors · forearms</v>
+      </c>
+      <c r="H42" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Mantén las mancuernas cerca de las piernas y lleva la cadera atrás.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>conventional-deadlift</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Peso muerto convencional</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Peso muerto · Deadlift convencional</v>
+      </c>
+      <c r="D43" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E43" t="str">
+        <v>barbell_conventional_deadlift</v>
+      </c>
+      <c r="F43" t="str">
+        <v>glutes · hamstrings · spinal_erectors</v>
+      </c>
+      <c r="G43" t="str">
+        <v>quadriceps · upper_back · forearms</v>
+      </c>
+      <c r="H43" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Cadena posterior</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Prepara tensión antes de despegar la barra del suelo.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>trap-bar-deadlift</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Peso muerto con barra hexagonal</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Peso muerto trap bar · Peso muerto barra hexagonal</v>
+      </c>
+      <c r="D44" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E44" t="str">
+        <v>trap_bar_deadlift</v>
+      </c>
+      <c r="F44" t="str">
+        <v>glutes · quadriceps · hamstrings</v>
+      </c>
+      <c r="G44" t="str">
+        <v>spinal_erectors · forearms</v>
+      </c>
+      <c r="H44" t="str">
+        <v>trap_bar · plates</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Cadena posterior</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Mantén el torso firme y empuja el suelo con los pies.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>sumo-deadlift</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Peso muerto sumo</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Peso muerto estilo sumo</v>
+      </c>
+      <c r="D45" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E45" t="str">
+        <v>barbell_sumo_deadlift</v>
+      </c>
+      <c r="F45" t="str">
+        <v>glutes · adductors · hamstrings</v>
+      </c>
+      <c r="G45" t="str">
+        <v>quadriceps · spinal_erectors</v>
+      </c>
+      <c r="H45" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Cadena posterior</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Mantén las rodillas alineadas con los pies y la barra cerca.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>leg-curl</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Curl femoral sentado</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Curl femoral · Curl femoral máquina</v>
+      </c>
+      <c r="D46" t="str">
+        <v>knee_flexion</v>
+      </c>
+      <c r="E46" t="str">
+        <v>seated_leg_curl</v>
+      </c>
+      <c r="F46" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="G46" t="str">
+        <v>calves</v>
+      </c>
+      <c r="H46" t="str">
+        <v>seated_leg_curl</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Evita levantar la cadera.</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>lying-leg-curl</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Curl femoral tumbado</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Curl femoral acostado</v>
+      </c>
+      <c r="D47" t="str">
+        <v>knee_flexion</v>
+      </c>
+      <c r="E47" t="str">
+        <v>lying_leg_curl</v>
+      </c>
+      <c r="F47" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="G47" t="str">
+        <v>calves</v>
+      </c>
+      <c r="H47" t="str">
+        <v>lying_leg_curl</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Mantén la pelvis apoyada durante toda la repetición.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>single-leg-curl</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Curl femoral unilateral</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Curl femoral a una pierna</v>
+      </c>
+      <c r="D48" t="str">
+        <v>knee_flexion</v>
+      </c>
+      <c r="E48" t="str">
+        <v>single_leg_machine_curl</v>
+      </c>
+      <c r="F48" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="G48" t="str">
+        <v>calves</v>
+      </c>
+      <c r="H48" t="str">
+        <v>seated_leg_curl</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Completa el recorrido sin girar la pelvis.</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>cable-pull-through</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Pull through en polea</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Pull through · Jalón de cadera en polea</v>
+      </c>
+      <c r="D49" t="str">
+        <v>hip_hinge</v>
+      </c>
+      <c r="E49" t="str">
+        <v>cable_pull_through</v>
+      </c>
+      <c r="F49" t="str">
+        <v>glutes · hamstrings</v>
+      </c>
+      <c r="G49" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="H49" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Deja que la cadera viaje atrás y termina contrayendo glúteos.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>machine-hip-abduction</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Abducción de cadera en máquina</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Abductores en máquina · Máquina de abductores</v>
+      </c>
+      <c r="D50" t="str">
+        <v>hip_abduction</v>
+      </c>
+      <c r="E50" t="str">
+        <v>machine_hip_abduction</v>
+      </c>
+      <c r="F50" t="str">
+        <v>gluteus_medius · gluteus_minimus</v>
+      </c>
+      <c r="G50" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="H50" t="str">
+        <v>hip_abduction_machine</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Mantén la pelvis estable y evita impulsos.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>cable-hip-abduction</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Abducción de cadera en polea</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Abducción en polea · Patada lateral en polea</v>
+      </c>
+      <c r="D51" t="str">
+        <v>hip_abduction</v>
+      </c>
+      <c r="E51" t="str">
+        <v>standing_cable_hip_abduction</v>
+      </c>
+      <c r="F51" t="str">
+        <v>gluteus_medius · gluteus_minimus</v>
+      </c>
+      <c r="G51" t="str">
+        <v>glutes</v>
+      </c>
+      <c r="H51" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Glúteos</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Mueve la pierna sin inclinar el tronco.</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>machine-hip-adduction</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Aducción de cadera en máquina</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Aductores en máquina · Máquina de aductores</v>
+      </c>
+      <c r="D52" t="str">
+        <v>hip_adduction</v>
+      </c>
+      <c r="E52" t="str">
+        <v>machine_hip_adduction</v>
+      </c>
+      <c r="F52" t="str">
+        <v>adductors</v>
+      </c>
+      <c r="G52" t="str">
+        <v>gracilis</v>
+      </c>
+      <c r="H52" t="str">
+        <v>hip_adduction_machine</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Aductores</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Cierra las piernas con control y sin rebotes.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>nordic-hamstring-curl</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Curl nórdico de isquios</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Curl nórdico · Nordic curl</v>
+      </c>
+      <c r="D53" t="str">
+        <v>knee_flexion</v>
+      </c>
+      <c r="E53" t="str">
+        <v>nordic_hamstring_curl</v>
+      </c>
+      <c r="F53" t="str">
+        <v>hamstrings</v>
+      </c>
+      <c r="G53" t="str">
+        <v>glutes · calves</v>
+      </c>
+      <c r="H53" t="str">
+        <v>nordic_bench</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Isquios</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Desciende solo hasta donde puedas mantener la cadera extendida.</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>overhead-press</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Press militar</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Press militar con barra</v>
+      </c>
+      <c r="D54" t="str">
+        <v>vertical_push</v>
+      </c>
+      <c r="E54" t="str">
+        <v>standing_barbell_overhead_press</v>
+      </c>
+      <c r="F54" t="str">
+        <v>deltoids</v>
+      </c>
+      <c r="G54" t="str">
+        <v>triceps · upper_chest</v>
+      </c>
+      <c r="H54" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Aprieta glúteos y abdomen.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>db-shoulder-press</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Press de hombros con mancuernas</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Press hombro mancuernas · Press sentado con mancuernas</v>
+      </c>
+      <c r="D55" t="str">
+        <v>vertical_push</v>
+      </c>
+      <c r="E55" t="str">
+        <v>seated_dumbbell_shoulder_press</v>
+      </c>
+      <c r="F55" t="str">
+        <v>deltoids</v>
+      </c>
+      <c r="G55" t="str">
+        <v>triceps · upper_chest</v>
+      </c>
+      <c r="H55" t="str">
+        <v>dumbbells · adjustable_bench</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Mantén los antebrazos verticales y evita arquear la espalda.</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>machine-shoulder-press</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Press de hombros en máquina</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Press hombro máquina</v>
+      </c>
+      <c r="D56" t="str">
+        <v>vertical_push</v>
+      </c>
+      <c r="E56" t="str">
+        <v>machine_shoulder_press</v>
+      </c>
+      <c r="F56" t="str">
+        <v>deltoids</v>
+      </c>
+      <c r="G56" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="H56" t="str">
+        <v>shoulder_press_machine</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Ajusta el asiento para empezar con las manos cerca de los hombros.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>arnold-press</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Press Arnold</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Press Arnold con mancuernas</v>
+      </c>
+      <c r="D57" t="str">
+        <v>vertical_push</v>
+      </c>
+      <c r="E57" t="str">
+        <v>dumbbell_arnold_press</v>
+      </c>
+      <c r="F57" t="str">
+        <v>deltoids</v>
+      </c>
+      <c r="G57" t="str">
+        <v>triceps · upper_chest</v>
+      </c>
+      <c r="H57" t="str">
+        <v>dumbbells · adjustable_bench</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Rota de forma suave sin forzar el hombro.</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>lateral-raise</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Elevaciones laterales</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Elevación lateral</v>
+      </c>
+      <c r="D58" t="str">
+        <v>shoulder_abduction</v>
+      </c>
+      <c r="E58" t="str">
+        <v>dumbbell_lateral_raise</v>
+      </c>
+      <c r="F58" t="str">
+        <v>lateral_deltoid</v>
+      </c>
+      <c r="G58" t="str">
+        <v>upper_traps</v>
+      </c>
+      <c r="H58" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Sube con control.</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>cable-lateral-raise</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Elevación lateral en polea</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Elevaciones laterales en polea</v>
+      </c>
+      <c r="D59" t="str">
+        <v>shoulder_abduction</v>
+      </c>
+      <c r="E59" t="str">
+        <v>single_arm_cable_lateral_raise</v>
+      </c>
+      <c r="F59" t="str">
+        <v>lateral_deltoid</v>
+      </c>
+      <c r="G59" t="str">
+        <v>upper_traps</v>
+      </c>
+      <c r="H59" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Mantén tensión continua y evita elevar el hombro.</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>machine-lateral-raise</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Elevación lateral en máquina</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Laterales en máquina · Máquina de deltoide lateral</v>
+      </c>
+      <c r="D60" t="str">
+        <v>shoulder_abduction</v>
+      </c>
+      <c r="E60" t="str">
+        <v>machine_lateral_raise</v>
+      </c>
+      <c r="F60" t="str">
+        <v>lateral_deltoid</v>
+      </c>
+      <c r="G60" t="str">
+        <v>upper_traps</v>
+      </c>
+      <c r="H60" t="str">
+        <v>lateral_raise_machine</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Alinea el hombro con el eje de la máquina.</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>front-raise</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Elevación frontal con mancuernas</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Elevaciones frontales</v>
+      </c>
+      <c r="D61" t="str">
+        <v>shoulder_flexion</v>
+      </c>
+      <c r="E61" t="str">
+        <v>dumbbell_front_raise</v>
+      </c>
+      <c r="F61" t="str">
+        <v>anterior_deltoid</v>
+      </c>
+      <c r="G61" t="str">
+        <v>upper_chest</v>
+      </c>
+      <c r="H61" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Eleva hasta una altura cómoda sin balancear el tronco.</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>rear-delt-fly</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Pájaros con mancuernas</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Aperturas posteriores · Elevación posterior</v>
+      </c>
+      <c r="D62" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E62" t="str">
+        <v>dumbbell_rear_delt_fly</v>
+      </c>
+      <c r="F62" t="str">
+        <v>posterior_deltoid</v>
+      </c>
+      <c r="G62" t="str">
+        <v>upper_back</v>
+      </c>
+      <c r="H62" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Abre los brazos sin encoger los hombros.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>reverse-pec-deck</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Pájaros en peck deck</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Peck deck inverso · Reverse fly máquina</v>
+      </c>
+      <c r="D63" t="str">
+        <v>horizontal_pull</v>
+      </c>
+      <c r="E63" t="str">
+        <v>machine_reverse_fly</v>
+      </c>
+      <c r="F63" t="str">
+        <v>posterior_deltoid</v>
+      </c>
+      <c r="G63" t="str">
+        <v>upper_back · rotator_cuff</v>
+      </c>
+      <c r="H63" t="str">
+        <v>pec_deck</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Mantén el pecho apoyado y abre desde el hombro.</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>upright-row</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Remo al mentón</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Remo vertical · Upright row</v>
+      </c>
+      <c r="D64" t="str">
+        <v>shoulder_abduction</v>
+      </c>
+      <c r="E64" t="str">
+        <v>barbell_upright_row</v>
+      </c>
+      <c r="F64" t="str">
+        <v>lateral_deltoid · upper_traps</v>
+      </c>
+      <c r="G64" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="H64" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Usa un agarre cómodo y no subas por encima de un rango sin dolor.</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>cable-external-rotation</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Rotación externa de hombro en polea</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Rotación externa en polea</v>
+      </c>
+      <c r="D65" t="str">
+        <v>shoulder_external_rotation</v>
+      </c>
+      <c r="E65" t="str">
+        <v>cable_external_rotation</v>
+      </c>
+      <c r="F65" t="str">
+        <v>rotator_cuff</v>
+      </c>
+      <c r="G65" t="str">
+        <v>posterior_deltoid</v>
+      </c>
+      <c r="H65" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Hombros</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Mantén el codo pegado al cuerpo y usa poca carga.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>biceps-curl</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Curl de bíceps con mancuernas</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Curl de bíceps · Curl bíceps</v>
+      </c>
+      <c r="D66" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E66" t="str">
+        <v>standing_dumbbell_curl</v>
+      </c>
+      <c r="F66" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G66" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H66" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Evita balancear el tronco.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>barbell-curl</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Curl de bíceps con barra</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Curl con barra · Curl barra recta</v>
+      </c>
+      <c r="D67" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E67" t="str">
+        <v>barbell_biceps_curl</v>
+      </c>
+      <c r="F67" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G67" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H67" t="str">
+        <v>barbell · plates</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Mantén los codos cerca del tronco.</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>ez-bar-curl</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Curl de bíceps con barra EZ</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Curl barra Z · Curl barra EZ</v>
+      </c>
+      <c r="D68" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E68" t="str">
+        <v>ez_bar_biceps_curl</v>
+      </c>
+      <c r="F68" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G68" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H68" t="str">
+        <v>ez_bar · plates</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Barra EZ</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Usa el agarre que mantenga las muñecas cómodas.</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>hammer-curl</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Curl martillo</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Curl neutro · Martillo con mancuernas</v>
+      </c>
+      <c r="D69" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E69" t="str">
+        <v>dumbbell_hammer_curl</v>
+      </c>
+      <c r="F69" t="str">
+        <v>brachialis · biceps</v>
+      </c>
+      <c r="G69" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H69" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Mantén las palmas enfrentadas durante todo el recorrido.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>incline-db-curl</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Curl inclinado con mancuernas</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Curl bíceps banco inclinado</v>
+      </c>
+      <c r="D70" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E70" t="str">
+        <v>incline_dumbbell_curl</v>
+      </c>
+      <c r="F70" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G70" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H70" t="str">
+        <v>dumbbells · adjustable_bench</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Mantén los hombros atrás y evita adelantarlos.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>preacher-curl</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Curl predicador</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Curl Scott · Predicador</v>
+      </c>
+      <c r="D71" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E71" t="str">
+        <v>preacher_curl</v>
+      </c>
+      <c r="F71" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G71" t="str">
+        <v>brachialis · forearms</v>
+      </c>
+      <c r="H71" t="str">
+        <v>ez_bar · plates · preacher_bench</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Barra EZ</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Mantén el brazo apoyado y no hiperextiendas el codo.</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>cable-curl</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Curl de bíceps en polea</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Curl polea · Curl cable</v>
+      </c>
+      <c r="D72" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E72" t="str">
+        <v>cable_biceps_curl</v>
+      </c>
+      <c r="F72" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G72" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H72" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Evita mover los hombros y mantén tensión continua.</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>concentration-curl</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Curl concentrado</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Curl concentración</v>
+      </c>
+      <c r="D73" t="str">
+        <v>elbow_flexion</v>
+      </c>
+      <c r="E73" t="str">
+        <v>seated_concentration_curl</v>
+      </c>
+      <c r="F73" t="str">
+        <v>biceps</v>
+      </c>
+      <c r="G73" t="str">
+        <v>forearms</v>
+      </c>
+      <c r="H73" t="str">
+        <v>dumbbells · bench</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Bíceps</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Apoya el brazo y completa el recorrido sin impulso.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>triceps-pushdown</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Extensión de tríceps en polea con barra</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Extensión de tríceps en polea · Tríceps polea</v>
+      </c>
+      <c r="D74" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E74" t="str">
+        <v>straight_bar_pushdown</v>
+      </c>
+      <c r="F74" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Mantén los codos pegados.</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>rope-pushdown</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Extensión de tríceps con cuerda</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Tríceps cuerda · Pushdown con cuerda</v>
+      </c>
+      <c r="D75" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E75" t="str">
+        <v>rope_triceps_pushdown</v>
+      </c>
+      <c r="F75" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Separa los extremos de la cuerda al final sin mover los codos.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>overhead-cable-extension</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Extensión de tríceps sobre la cabeza en polea</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Tríceps overhead en polea · Extensión francesa en polea</v>
+      </c>
+      <c r="D76" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E76" t="str">
+        <v>overhead_cable_triceps_extension</v>
+      </c>
+      <c r="F76" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G76" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="H76" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Mantén los codos orientados al frente y las costillas controladas.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>skull-crusher</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Press francés tumbado con barra EZ</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Rompecráneos · Skull crusher · Press francés</v>
+      </c>
+      <c r="D77" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E77" t="str">
+        <v>lying_ez_bar_triceps_extension</v>
+      </c>
+      <c r="F77" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>ez_bar · plates · bench</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Barra EZ</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Mueve desde el codo y evita abrirlos en exceso.</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>close-grip-bench-press</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Press de banca con agarre cerrado</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Press cerrado · Press banca cerrado</v>
+      </c>
+      <c r="D78" t="str">
+        <v>horizontal_push</v>
+      </c>
+      <c r="E78" t="str">
+        <v>close_grip_bench_press</v>
+      </c>
+      <c r="F78" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G78" t="str">
+        <v>chest · anterior_deltoid</v>
+      </c>
+      <c r="H78" t="str">
+        <v>barbell · plates · bench · squat_rack</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Barra</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Usa un agarre cómodo y mantén los codos controlados.</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>triceps-dip</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Fondos para tríceps</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Fondos de tríceps · Fondos verticales</v>
+      </c>
+      <c r="D79" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E79" t="str">
+        <v>bodyweight_triceps_dip</v>
+      </c>
+      <c r="F79" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G79" t="str">
+        <v>chest · anterior_deltoid</v>
+      </c>
+      <c r="H79" t="str">
+        <v>dip_station</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Mantén el tronco más vertical y evita una profundidad dolorosa.</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>single-arm-cable-extension</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Extensión de tríceps unilateral en polea</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Tríceps unilateral en polea</v>
+      </c>
+      <c r="D80" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E80" t="str">
+        <v>single_arm_cable_pushdown</v>
+      </c>
+      <c r="F80" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Mantén el hombro estable y extiende por completo sin impulso.</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>db-overhead-triceps-extension</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Extensión de tríceps sobre la cabeza con mancuerna</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Copa de tríceps · Extensión overhead con mancuerna</v>
+      </c>
+      <c r="D81" t="str">
+        <v>elbow_extension</v>
+      </c>
+      <c r="E81" t="str">
+        <v>dumbbell_overhead_triceps_extension</v>
+      </c>
+      <c r="F81" t="str">
+        <v>triceps</v>
+      </c>
+      <c r="G81" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="H81" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Tríceps</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Mantén las costillas controladas y evita abrir demasiado los codos.</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>calf-raise</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Elevación de gemelos en máquina</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Gemelo máquina</v>
+      </c>
+      <c r="D82" t="str">
+        <v>calf_raise</v>
+      </c>
+      <c r="E82" t="str">
+        <v>machine_calf_raise</v>
+      </c>
+      <c r="F82" t="str">
+        <v>calves</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>calf_raise_machine</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Gemelos</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Busca recorrido completo.</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>standing-calf-raise</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Elevación de gemelos de pie</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Gemelos de pie</v>
+      </c>
+      <c r="D83" t="str">
+        <v>calf_raise</v>
+      </c>
+      <c r="E83" t="str">
+        <v>standing_calf_raise</v>
+      </c>
+      <c r="F83" t="str">
+        <v>calves</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>dumbbells · step</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Gemelos</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Pausa arriba y baja el talón con control.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>seated-calf-raise</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Elevación de gemelos sentado</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Gemelo sentado · Sóleo sentado</v>
+      </c>
+      <c r="D84" t="str">
+        <v>calf_raise</v>
+      </c>
+      <c r="E84" t="str">
+        <v>seated_calf_raise</v>
+      </c>
+      <c r="F84" t="str">
+        <v>calves</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>seated_calf_raise_machine</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Gemelos</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Mantén la almohadilla estable sobre los muslos.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>leg-press-calf-raise</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Elevación de gemelos en prensa</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Gemelos en prensa</v>
+      </c>
+      <c r="D85" t="str">
+        <v>calf_raise</v>
+      </c>
+      <c r="E85" t="str">
+        <v>leg_press_calf_raise</v>
+      </c>
+      <c r="F85" t="str">
+        <v>calves</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>leg_press</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Gemelos</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Máquina</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Mueve solo el tobillo y mantén las rodillas estables.</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>plank</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Plancha</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Plancha frontal</v>
+      </c>
+      <c r="D86" t="str">
+        <v>anti_extension_core</v>
+      </c>
+      <c r="E86" t="str">
+        <v>forearm_plank</v>
+      </c>
+      <c r="F86" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="G86" t="str">
+        <v>shoulders · glutes</v>
+      </c>
+      <c r="H86" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Mantén la pelvis neutra.</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>side-plank</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Plancha lateral</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Plancha de lado</v>
+      </c>
+      <c r="D87" t="str">
+        <v>lateral_core</v>
+      </c>
+      <c r="E87" t="str">
+        <v>side_plank</v>
+      </c>
+      <c r="F87" t="str">
+        <v>obliques · trunk</v>
+      </c>
+      <c r="G87" t="str">
+        <v>gluteus_medius · shoulders</v>
+      </c>
+      <c r="H87" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Mantén cadera, hombros y pies alineados.</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>dead-bug</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Dead bug</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Bicho muerto</v>
+      </c>
+      <c r="D88" t="str">
+        <v>anti_extension_core</v>
+      </c>
+      <c r="E88" t="str">
+        <v>dead_bug</v>
+      </c>
+      <c r="F88" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="G88" t="str">
+        <v>hip_flexors</v>
+      </c>
+      <c r="H88" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Mantén la zona lumbar estable mientras alternas brazos y piernas.</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>bird-dog</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Bird dog</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Perro de caza · Extensión contralateral en cuadrupedia</v>
+      </c>
+      <c r="D89" t="str">
+        <v>anti_rotation_core</v>
+      </c>
+      <c r="E89" t="str">
+        <v>quadruped_bird_dog</v>
+      </c>
+      <c r="F89" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="G89" t="str">
+        <v>glutes · shoulders · spinal_erectors</v>
+      </c>
+      <c r="H89" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Extiende brazo y pierna sin girar la pelvis.</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>pallof-press</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Press Pallof</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Pallof press · Antirrotación en polea</v>
+      </c>
+      <c r="D90" t="str">
+        <v>anti_rotation_core</v>
+      </c>
+      <c r="E90" t="str">
+        <v>standing_pallof_press</v>
+      </c>
+      <c r="F90" t="str">
+        <v>trunk · obliques</v>
+      </c>
+      <c r="G90" t="str">
+        <v>shoulders</v>
+      </c>
+      <c r="H90" t="str">
+        <v>cable_machine</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Resiste la rotación y mantén el tronco inmóvil.</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>cable-crunch</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Crunch en polea</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Encogimiento en polea</v>
+      </c>
+      <c r="D91" t="str">
+        <v>trunk_flexion</v>
+      </c>
+      <c r="E91" t="str">
+        <v>kneeling_cable_crunch</v>
+      </c>
+      <c r="F91" t="str">
+        <v>rectus_abdominis</v>
+      </c>
+      <c r="G91" t="str">
+        <v>obliques</v>
+      </c>
+      <c r="H91" t="str">
+        <v>cable_machine · mat</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Polea</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Hipertrofia</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Flexiona el tronco sin tirar con los brazos.</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>reverse-crunch</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Crunch inverso</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Encogimiento inverso</v>
+      </c>
+      <c r="D92" t="str">
+        <v>trunk_flexion</v>
+      </c>
+      <c r="E92" t="str">
+        <v>reverse_crunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>rectus_abdominis</v>
+      </c>
+      <c r="G92" t="str">
+        <v>obliques · hip_flexors</v>
+      </c>
+      <c r="H92" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J92" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Core</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Eleva la pelvis con control sin balancear las piernas.</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>hanging-knee-raise</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Elevación de rodillas colgado</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Rodillas al pecho colgado</v>
+      </c>
+      <c r="D93" t="str">
+        <v>hip_flexion_core</v>
+      </c>
+      <c r="E93" t="str">
+        <v>hanging_knee_raise</v>
+      </c>
+      <c r="F93" t="str">
+        <v>rectus_abdominis · hip_flexors</v>
+      </c>
+      <c r="G93" t="str">
+        <v>forearms · latissimus_dorsi</v>
+      </c>
+      <c r="H93" t="str">
+        <v>pull_up_bar</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Peso corporal</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Evita balancearte y eleva la pelvis al final.</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>ab-wheel-rollout</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Rueda abdominal</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Ab wheel · Rollout abdominal</v>
+      </c>
+      <c r="D94" t="str">
+        <v>anti_extension_core</v>
+      </c>
+      <c r="E94" t="str">
+        <v>kneeling_ab_wheel_rollout</v>
+      </c>
+      <c r="F94" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="G94" t="str">
+        <v>latissimus_dorsi · shoulders</v>
+      </c>
+      <c r="H94" t="str">
+        <v>ab_wheel · mat</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Core</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Rueda abdominal</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Avanza solo hasta donde puedas mantener la pelvis y las costillas controladas.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>farmer-carry</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Paseo del granjero</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Farmer walk · Caminata del granjero</v>
+      </c>
+      <c r="D95" t="str">
+        <v>loaded_carry</v>
+      </c>
+      <c r="E95" t="str">
+        <v>bilateral_farmer_carry</v>
+      </c>
+      <c r="F95" t="str">
+        <v>forearms · upper_traps · trunk</v>
+      </c>
+      <c r="G95" t="str">
+        <v>glutes · calves · shoulders</v>
+      </c>
+      <c r="H95" t="str">
+        <v>dumbbells</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Cuerpo completo</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Mancuernas</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Fuerza</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Camina erguido sin inclinarte ni encoger los hombros.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>treadmill-walk</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Caminata en cinta</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Andar en cinta · Cinta caminando</v>
+      </c>
+      <c r="D96" t="str">
+        <v>locomotion</v>
+      </c>
+      <c r="E96" t="str">
+        <v>treadmill_walking</v>
+      </c>
+      <c r="F96" t="str">
+        <v>cardiorespiratory</v>
+      </c>
+      <c r="G96" t="str">
+        <v>quadriceps · glutes · calves</v>
+      </c>
+      <c r="H96" t="str">
+        <v>treadmill</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Cinta</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Usa una velocidad e inclinación que permitan mantener una técnica cómoda.</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>stationary-bike</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Bicicleta estática</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Bici estática · Bicicleta indoor</v>
+      </c>
+      <c r="D97" t="str">
+        <v>locomotion</v>
+      </c>
+      <c r="E97" t="str">
+        <v>stationary_cycling</v>
+      </c>
+      <c r="F97" t="str">
+        <v>cardiorespiratory</v>
+      </c>
+      <c r="G97" t="str">
+        <v>quadriceps · glutes · calves</v>
+      </c>
+      <c r="H97" t="str">
+        <v>stationary_bike</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Bicicleta</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Ajusta el sillín para pedalear sin bloquear la rodilla.</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>elliptical</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Elíptica</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Máquina elíptica</v>
+      </c>
+      <c r="D98" t="str">
+        <v>locomotion</v>
+      </c>
+      <c r="E98" t="str">
+        <v>elliptical_training</v>
+      </c>
+      <c r="F98" t="str">
+        <v>cardiorespiratory</v>
+      </c>
+      <c r="G98" t="str">
+        <v>quadriceps · glutes · calves</v>
+      </c>
+      <c r="H98" t="str">
+        <v>elliptical</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Elíptica</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Cardio</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Mantén una cadencia estable y el tronco erguido.</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>cat-cow</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Gato-vaca</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Cat cow · Gato vaca</v>
+      </c>
+      <c r="D99" t="str">
+        <v>spinal_mobility</v>
+      </c>
+      <c r="E99" t="str">
+        <v>quadruped_cat_cow</v>
+      </c>
+      <c r="F99" t="str">
+        <v>spinal_mobility</v>
+      </c>
+      <c r="G99" t="str">
+        <v>trunk</v>
+      </c>
+      <c r="H99" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Esterilla</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Alterna flexión y extensión suave sin forzar el rango.</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>thoracic-rotation</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Rotación torácica en cuadrupedia</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Rotación torácica · Open book cuadrupedia</v>
+      </c>
+      <c r="D100" t="str">
+        <v>thoracic_rotation</v>
+      </c>
+      <c r="E100" t="str">
+        <v>quadruped_thoracic_rotation</v>
+      </c>
+      <c r="F100" t="str">
+        <v>thoracic_spine</v>
+      </c>
+      <c r="G100" t="str">
+        <v>shoulders · trunk</v>
+      </c>
+      <c r="H100" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Esterilla</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Rota desde la zona torácica sin desplazar la pelvis.</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>hip-flexor-stretch</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Estiramiento de flexores de cadera</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Estiramiento psoas · Estiramiento flexor de cadera</v>
+      </c>
+      <c r="D101" t="str">
+        <v>hip_flexor_mobility</v>
+      </c>
+      <c r="E101" t="str">
+        <v>half_kneeling_hip_flexor_stretch</v>
+      </c>
+      <c r="F101" t="str">
+        <v>hip_flexors</v>
+      </c>
+      <c r="G101" t="str">
+        <v>quadriceps</v>
+      </c>
+      <c r="H101" t="str">
+        <v>bodyweight · mat</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Esterilla</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Movilidad</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Mantén la pelvis neutra y avanza suavemente.</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L101"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A3"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
@@ -662,7 +4560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <cols>

--- a/plantilla-rutina-gymos.xlsx
+++ b/plantilla-rutina-gymos.xlsx
@@ -461,7 +461,7 @@
         <v>Biblioteca</v>
       </c>
       <c r="B6" t="str">
-        <v>Selecciona ejercicios de Biblioteca: no inventes uno si allí existe una alternativa válida. Copia exactamente Ejercicio y _GymOS exercise en Rutina.</v>
+        <v>Selecciona ejercicios de Biblioteca: no inventes uno si allí existe una alternativa válida. Copia _GymOS exercise y Ejercicio cuando puedas.</v>
       </c>
     </row>
     <row r="7">
@@ -469,7 +469,7 @@
         <v>IDs</v>
       </c>
       <c r="B7" t="str">
-        <v>No traduzcas, abrevies ni modifiques IDs. Si el ejercicio no aparece en Biblioteca, deja _GymOS exercise vacío y conserva su nombre para el flujo existente.</v>
+        <v>_GymOS exercise es el identificador contractual: no lo traduzcas, abrevies, modifiques ni inventes. Ejercicio es descriptivo y GymOS puede normalizarlo automáticamente cuando el ID es válido.</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>ChatGPT</v>
       </c>
       <c r="B8" t="str">
-        <v>Puede ayudarte a rellenar Sesiones y Rutina, pero debe respetar nombres, IDs, columnas y estructura de esta plantilla.</v>
+        <v>Puede ayudarte a rellenar Sesiones y Rutina. Debe copiar el ID y el nombre desde Biblioteca cuando pueda, respetando columnas y estructura.</v>
       </c>
     </row>
     <row r="9">

--- a/plantilla-rutina-gymos.xlsx
+++ b/plantilla-rutina-gymos.xlsx
@@ -469,7 +469,7 @@
         <v>IDs</v>
       </c>
       <c r="B7" t="str">
-        <v>_GymOS exercise es el identificador contractual: no lo traduzcas, abrevies, modifiques ni inventes. Ejercicio es descriptivo y GymOS puede normalizarlo automáticamente cuando el ID es válido.</v>
+        <v>_GymOS exercise es la única identidad autoritativa: no lo traduzcas, abrevies, modifiques ni inventes. Ejercicio es descriptivo; si no coincide, GymOS lo reemplaza por el nombre oficial del ID válido, aunque el texto corresponda a otro ejercicio conocido.</v>
       </c>
     </row>
     <row r="8">
